--- a/Lab_4/data/partB/param_optimization_process/v200_k20_s150_results.xlsx
+++ b/Lab_4/data/partB/param_optimization_process/v200_k20_s150_results.xlsx
@@ -518,49 +518,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="n">
         <v>2</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
         <v>1</v>
       </c>
-      <c r="K2" t="n">
-        <v>4</v>
-      </c>
       <c r="L2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="N2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -570,19 +570,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C3" t="n">
         <v>61</v>
       </c>
       <c r="D3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F3" t="n">
         <v>0</v>
-      </c>
-      <c r="E3" t="n">
-        <v>6</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
@@ -591,16 +591,16 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -609,10 +609,10 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -628,7 +628,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -652,7 +652,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -674,22 +674,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -698,19 +698,19 @@
         <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -729,43 +729,43 @@
         <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F6" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G6" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
+        <v>11</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>3</v>
+      </c>
+      <c r="M6" t="n">
+        <v>11</v>
+      </c>
+      <c r="N6" t="n">
         <v>8</v>
       </c>
-      <c r="J6" t="n">
-        <v>2</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M6" t="n">
-        <v>17</v>
-      </c>
-      <c r="N6" t="n">
-        <v>5</v>
-      </c>
       <c r="O6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P6" t="n">
         <v>7</v>
@@ -778,7 +778,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -790,16 +790,16 @@
         <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G7" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -808,19 +808,19 @@
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -842,16 +842,16 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
+        <v>5</v>
+      </c>
+      <c r="G8" t="n">
         <v>7</v>
       </c>
-      <c r="G8" t="n">
-        <v>13</v>
-      </c>
       <c r="H8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I8" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -860,19 +860,19 @@
         <v>11</v>
       </c>
       <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>9</v>
+      </c>
+      <c r="N8" t="n">
         <v>1</v>
       </c>
-      <c r="M8" t="n">
-        <v>7</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -894,28 +894,28 @@
         <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I9" t="n">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="N9" t="n">
         <v>1</v>
@@ -924,7 +924,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -940,10 +940,10 @@
         <v>7</v>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -958,19 +958,19 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -986,7 +986,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -998,37 +998,37 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G11" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>41</v>
+      </c>
+      <c r="J11" t="n">
         <v>0</v>
       </c>
-      <c r="I11" t="n">
-        <v>35</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
       <c r="K11" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
+        <v>3</v>
+      </c>
+      <c r="N11" t="n">
         <v>2</v>
       </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
         <v>0</v>
       </c>
-      <c r="O11" t="n">
-        <v>1</v>
-      </c>
       <c r="P11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1041,13 +1041,13 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D12" t="n">
         <v>7</v>
       </c>
       <c r="E12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F12" t="n">
         <v>1</v>
@@ -1062,19 +1062,19 @@
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1090,22 +1090,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G13" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1114,25 +1114,25 @@
         <v>6</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="N13" t="n">
+        <v>8</v>
+      </c>
+      <c r="O13" t="n">
         <v>4</v>
       </c>
-      <c r="O13" t="n">
-        <v>5</v>
-      </c>
       <c r="P13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1142,19 +1142,19 @@
         </is>
       </c>
       <c r="B14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" t="n">
         <v>1</v>
       </c>
-      <c r="C14" t="n">
-        <v>5</v>
-      </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G14" t="n">
         <v>7</v>
@@ -1166,25 +1166,25 @@
         <v>4</v>
       </c>
       <c r="J14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N14" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P14" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -1200,40 +1200,40 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J15" t="n">
+        <v>2</v>
+      </c>
+      <c r="K15" t="n">
         <v>1</v>
       </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
       <c r="L15" t="n">
+        <v>4</v>
+      </c>
+      <c r="M15" t="n">
         <v>2</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P15" t="n">
         <v>1</v>
@@ -1249,16 +1249,16 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" t="n">
         <v>2</v>
       </c>
-      <c r="D16" t="n">
-        <v>1</v>
-      </c>
       <c r="E16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F16" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G16" t="n">
         <v>9</v>
@@ -1267,28 +1267,28 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O16" t="n">
         <v>2</v>
       </c>
       <c r="P16" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -1828,7 +1828,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1845,7 +1845,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1998,7 +1998,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2117,7 +2117,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2372,7 +2372,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2593,7 +2593,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2678,7 +2678,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -2712,7 +2712,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2746,7 +2746,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2967,7 +2967,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -3052,7 +3052,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3137,7 +3137,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -3154,7 +3154,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3596,7 +3596,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -3664,7 +3664,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -3732,7 +3732,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3919,7 +3919,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -4038,7 +4038,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -4089,7 +4089,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4140,7 +4140,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -4157,7 +4157,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -4174,7 +4174,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4225,7 +4225,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -4344,7 +4344,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -4429,7 +4429,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4463,7 +4463,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4497,7 +4497,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -4548,7 +4548,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4616,7 +4616,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -4922,7 +4922,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -5381,7 +5381,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -5823,7 +5823,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -6163,7 +6163,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -6401,7 +6401,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -6435,7 +6435,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6469,7 +6469,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6537,7 +6537,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -6673,7 +6673,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -6792,7 +6792,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -6877,7 +6877,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -6928,7 +6928,7 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -6979,7 +6979,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -7081,7 +7081,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -7098,7 +7098,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7217,7 +7217,7 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7234,7 +7234,7 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -7268,7 +7268,7 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7285,7 +7285,7 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7370,7 +7370,7 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7404,7 +7404,7 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -7421,7 +7421,7 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -7455,7 +7455,7 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -7523,7 +7523,7 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7642,7 +7642,7 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7676,7 +7676,7 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7693,7 +7693,7 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7744,7 +7744,7 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -7880,7 +7880,7 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7897,7 +7897,7 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7982,7 +7982,7 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7999,7 +7999,7 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -8050,7 +8050,7 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -8135,7 +8135,7 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8152,7 +8152,7 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -8220,7 +8220,7 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8288,7 +8288,7 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -8305,7 +8305,7 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -8339,7 +8339,7 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -8424,7 +8424,7 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8475,7 +8475,7 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -8577,7 +8577,7 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -8832,7 +8832,7 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8849,7 +8849,7 @@
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -8883,7 +8883,7 @@
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -8968,7 +8968,7 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9002,7 +9002,7 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -9019,7 +9019,7 @@
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -9070,7 +9070,7 @@
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9121,7 +9121,7 @@
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -9206,7 +9206,7 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -9325,7 +9325,7 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9342,7 +9342,7 @@
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9359,7 +9359,7 @@
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9444,7 +9444,7 @@
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -9495,7 +9495,7 @@
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -9546,7 +9546,7 @@
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -9631,7 +9631,7 @@
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -9733,7 +9733,7 @@
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -9784,7 +9784,7 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9818,7 +9818,7 @@
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -9835,7 +9835,7 @@
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -9903,7 +9903,7 @@
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -9954,7 +9954,7 @@
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9988,7 +9988,7 @@
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10005,7 +10005,7 @@
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -10124,7 +10124,7 @@
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -10243,7 +10243,7 @@
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -10311,7 +10311,7 @@
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -10413,7 +10413,7 @@
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -10447,7 +10447,7 @@
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10498,7 +10498,7 @@
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10532,7 +10532,7 @@
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -10617,7 +10617,7 @@
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10651,7 +10651,7 @@
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -10702,7 +10702,7 @@
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -11144,7 +11144,7 @@
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11161,7 +11161,7 @@
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -11212,7 +11212,7 @@
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -11246,7 +11246,7 @@
       </c>
       <c r="C585" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11314,7 +11314,7 @@
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11416,7 +11416,7 @@
       </c>
       <c r="C595" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11433,7 +11433,7 @@
       </c>
       <c r="C596" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11535,7 +11535,7 @@
       </c>
       <c r="C602" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11586,7 +11586,7 @@
       </c>
       <c r="C605" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -11637,7 +11637,7 @@
       </c>
       <c r="C608" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="C609" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -11671,7 +11671,7 @@
       </c>
       <c r="C610" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -11756,7 +11756,7 @@
       </c>
       <c r="C615" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11807,7 +11807,7 @@
       </c>
       <c r="C618" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -11841,7 +11841,7 @@
       </c>
       <c r="C620" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -11858,7 +11858,7 @@
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11875,7 +11875,7 @@
       </c>
       <c r="C622" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11926,7 +11926,7 @@
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -11977,7 +11977,7 @@
       </c>
       <c r="C628" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11994,7 +11994,7 @@
       </c>
       <c r="C629" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -12028,7 +12028,7 @@
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -12062,7 +12062,7 @@
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -12096,7 +12096,7 @@
       </c>
       <c r="C635" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12283,7 +12283,7 @@
       </c>
       <c r="C646" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -12436,7 +12436,7 @@
       </c>
       <c r="C655" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12453,7 +12453,7 @@
       </c>
       <c r="C656" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12470,7 +12470,7 @@
       </c>
       <c r="C657" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -12504,7 +12504,7 @@
       </c>
       <c r="C659" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -12521,7 +12521,7 @@
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12606,7 +12606,7 @@
       </c>
       <c r="C665" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -12674,7 +12674,7 @@
       </c>
       <c r="C669" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -12725,7 +12725,7 @@
       </c>
       <c r="C672" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -12810,7 +12810,7 @@
       </c>
       <c r="C677" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -12861,7 +12861,7 @@
       </c>
       <c r="C680" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -12980,7 +12980,7 @@
       </c>
       <c r="C687" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -13082,7 +13082,7 @@
       </c>
       <c r="C693" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -13116,7 +13116,7 @@
       </c>
       <c r="C695" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -13133,7 +13133,7 @@
       </c>
       <c r="C696" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13150,7 +13150,7 @@
       </c>
       <c r="C697" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -13184,7 +13184,7 @@
       </c>
       <c r="C699" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -13218,7 +13218,7 @@
       </c>
       <c r="C701" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13269,7 +13269,7 @@
       </c>
       <c r="C704" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -13286,7 +13286,7 @@
       </c>
       <c r="C705" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -13337,7 +13337,7 @@
       </c>
       <c r="C708" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13354,7 +13354,7 @@
       </c>
       <c r="C709" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13371,7 +13371,7 @@
       </c>
       <c r="C710" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13422,7 +13422,7 @@
       </c>
       <c r="C713" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13490,7 +13490,7 @@
       </c>
       <c r="C717" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13507,7 +13507,7 @@
       </c>
       <c r="C718" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -13592,7 +13592,7 @@
       </c>
       <c r="C723" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -13694,7 +13694,7 @@
       </c>
       <c r="C729" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -13762,7 +13762,7 @@
       </c>
       <c r="C733" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -13830,7 +13830,7 @@
       </c>
       <c r="C737" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13847,7 +13847,7 @@
       </c>
       <c r="C738" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -13966,7 +13966,7 @@
       </c>
       <c r="C745" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -14102,7 +14102,7 @@
       </c>
       <c r="C753" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14170,7 +14170,7 @@
       </c>
       <c r="C757" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14187,7 +14187,7 @@
       </c>
       <c r="C758" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -14238,7 +14238,7 @@
       </c>
       <c r="C761" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14272,7 +14272,7 @@
       </c>
       <c r="C763" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14289,7 +14289,7 @@
       </c>
       <c r="C764" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14374,7 +14374,7 @@
       </c>
       <c r="C769" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14391,7 +14391,7 @@
       </c>
       <c r="C770" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -14578,7 +14578,7 @@
       </c>
       <c r="C781" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -14663,7 +14663,7 @@
       </c>
       <c r="C786" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -14680,7 +14680,7 @@
       </c>
       <c r="C787" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14714,7 +14714,7 @@
       </c>
       <c r="C789" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -14765,7 +14765,7 @@
       </c>
       <c r="C792" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14833,7 +14833,7 @@
       </c>
       <c r="C796" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -14884,7 +14884,7 @@
       </c>
       <c r="C799" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14918,7 +14918,7 @@
       </c>
       <c r="C801" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C803" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15003,7 +15003,7 @@
       </c>
       <c r="C806" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15071,7 +15071,7 @@
       </c>
       <c r="C810" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15088,7 +15088,7 @@
       </c>
       <c r="C811" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15258,7 +15258,7 @@
       </c>
       <c r="C821" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15479,7 +15479,7 @@
       </c>
       <c r="C834" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -15496,7 +15496,7 @@
       </c>
       <c r="C835" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -15513,7 +15513,7 @@
       </c>
       <c r="C836" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15615,7 +15615,7 @@
       </c>
       <c r="C842" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -15734,7 +15734,7 @@
       </c>
       <c r="C849" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15785,7 +15785,7 @@
       </c>
       <c r="C852" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15853,7 +15853,7 @@
       </c>
       <c r="C856" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15904,7 +15904,7 @@
       </c>
       <c r="C859" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -15955,7 +15955,7 @@
       </c>
       <c r="C862" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -16023,7 +16023,7 @@
       </c>
       <c r="C866" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16074,7 +16074,7 @@
       </c>
       <c r="C869" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -16108,7 +16108,7 @@
       </c>
       <c r="C871" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -16193,7 +16193,7 @@
       </c>
       <c r="C876" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -16363,7 +16363,7 @@
       </c>
       <c r="C886" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16397,7 +16397,7 @@
       </c>
       <c r="C888" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -16448,7 +16448,7 @@
       </c>
       <c r="C891" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -16533,7 +16533,7 @@
       </c>
       <c r="C896" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -16601,7 +16601,7 @@
       </c>
       <c r="C900" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -16635,7 +16635,7 @@
       </c>
       <c r="C902" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -16669,7 +16669,7 @@
       </c>
       <c r="C904" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -16737,7 +16737,7 @@
       </c>
       <c r="C908" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -16771,7 +16771,7 @@
       </c>
       <c r="C910" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C918" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -16924,7 +16924,7 @@
       </c>
       <c r="C919" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -16958,7 +16958,7 @@
       </c>
       <c r="C921" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -16992,7 +16992,7 @@
       </c>
       <c r="C923" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17128,7 +17128,7 @@
       </c>
       <c r="C931" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17145,7 +17145,7 @@
       </c>
       <c r="C932" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -17162,7 +17162,7 @@
       </c>
       <c r="C933" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -17213,7 +17213,7 @@
       </c>
       <c r="C936" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17230,7 +17230,7 @@
       </c>
       <c r="C937" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17247,7 +17247,7 @@
       </c>
       <c r="C938" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -17281,7 +17281,7 @@
       </c>
       <c r="C940" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17298,7 +17298,7 @@
       </c>
       <c r="C941" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -17332,7 +17332,7 @@
       </c>
       <c r="C943" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -17417,7 +17417,7 @@
       </c>
       <c r="C948" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17434,7 +17434,7 @@
       </c>
       <c r="C949" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -17451,7 +17451,7 @@
       </c>
       <c r="C950" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17485,7 +17485,7 @@
       </c>
       <c r="C952" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17604,7 +17604,7 @@
       </c>
       <c r="C959" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17621,7 +17621,7 @@
       </c>
       <c r="C960" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17638,7 +17638,7 @@
       </c>
       <c r="C961" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -17672,7 +17672,7 @@
       </c>
       <c r="C963" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17689,7 +17689,7 @@
       </c>
       <c r="C964" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17842,7 +17842,7 @@
       </c>
       <c r="C973" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17859,7 +17859,7 @@
       </c>
       <c r="C974" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17876,7 +17876,7 @@
       </c>
       <c r="C975" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17944,7 +17944,7 @@
       </c>
       <c r="C979" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -17961,7 +17961,7 @@
       </c>
       <c r="C980" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17978,7 +17978,7 @@
       </c>
       <c r="C981" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -18131,7 +18131,7 @@
       </c>
       <c r="C990" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -18199,7 +18199,7 @@
       </c>
       <c r="C994" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -18267,7 +18267,7 @@
       </c>
       <c r="C998" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -18301,7 +18301,7 @@
       </c>
       <c r="C1000" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -18318,7 +18318,7 @@
       </c>
       <c r="C1001" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -18420,7 +18420,7 @@
       </c>
       <c r="C1007" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -18471,7 +18471,7 @@
       </c>
       <c r="C1010" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18522,7 +18522,7 @@
       </c>
       <c r="C1013" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -18573,7 +18573,7 @@
       </c>
       <c r="C1016" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18607,7 +18607,7 @@
       </c>
       <c r="C1018" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18658,7 +18658,7 @@
       </c>
       <c r="C1021" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18709,7 +18709,7 @@
       </c>
       <c r="C1024" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18726,7 +18726,7 @@
       </c>
       <c r="C1025" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -18743,7 +18743,7 @@
       </c>
       <c r="C1026" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="C1029" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18896,7 +18896,7 @@
       </c>
       <c r="C1035" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -18947,7 +18947,7 @@
       </c>
       <c r="C1038" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18998,7 +18998,7 @@
       </c>
       <c r="C1041" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19066,7 +19066,7 @@
       </c>
       <c r="C1045" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19134,7 +19134,7 @@
       </c>
       <c r="C1049" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -19236,7 +19236,7 @@
       </c>
       <c r="C1055" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19253,7 +19253,7 @@
       </c>
       <c r="C1056" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -19338,7 +19338,7 @@
       </c>
       <c r="C1061" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19389,7 +19389,7 @@
       </c>
       <c r="C1064" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -19406,7 +19406,7 @@
       </c>
       <c r="C1065" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19491,7 +19491,7 @@
       </c>
       <c r="C1070" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19576,7 +19576,7 @@
       </c>
       <c r="C1075" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19644,7 +19644,7 @@
       </c>
       <c r="C1079" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19797,7 +19797,7 @@
       </c>
       <c r="C1088" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19831,7 +19831,7 @@
       </c>
       <c r="C1090" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19967,7 +19967,7 @@
       </c>
       <c r="C1098" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -20086,7 +20086,7 @@
       </c>
       <c r="C1105" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -20154,7 +20154,7 @@
       </c>
       <c r="C1109" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -20239,7 +20239,7 @@
       </c>
       <c r="C1114" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20273,7 +20273,7 @@
       </c>
       <c r="C1116" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -20443,7 +20443,7 @@
       </c>
       <c r="C1126" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -20579,7 +20579,7 @@
       </c>
       <c r="C1134" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -20681,7 +20681,7 @@
       </c>
       <c r="C1140" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -20715,7 +20715,7 @@
       </c>
       <c r="C1142" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -20732,7 +20732,7 @@
       </c>
       <c r="C1143" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -20834,7 +20834,7 @@
       </c>
       <c r="C1149" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -20885,7 +20885,7 @@
       </c>
       <c r="C1152" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -20902,7 +20902,7 @@
       </c>
       <c r="C1153" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -20970,7 +20970,7 @@
       </c>
       <c r="C1157" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20987,7 +20987,7 @@
       </c>
       <c r="C1158" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -21055,7 +21055,7 @@
       </c>
       <c r="C1162" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -21140,7 +21140,7 @@
       </c>
       <c r="C1167" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -21276,7 +21276,7 @@
       </c>
       <c r="C1175" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21310,7 +21310,7 @@
       </c>
       <c r="C1177" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -21378,7 +21378,7 @@
       </c>
       <c r="C1181" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21582,7 +21582,7 @@
       </c>
       <c r="C1193" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21599,7 +21599,7 @@
       </c>
       <c r="C1194" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21701,7 +21701,7 @@
       </c>
       <c r="C1200" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21718,7 +21718,7 @@
       </c>
       <c r="C1201" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -21837,7 +21837,7 @@
       </c>
       <c r="C1208" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21888,7 +21888,7 @@
       </c>
       <c r="C1211" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -21922,7 +21922,7 @@
       </c>
       <c r="C1213" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22058,7 +22058,7 @@
       </c>
       <c r="C1221" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -22075,7 +22075,7 @@
       </c>
       <c r="C1222" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22109,7 +22109,7 @@
       </c>
       <c r="C1224" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22160,7 +22160,7 @@
       </c>
       <c r="C1227" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22194,7 +22194,7 @@
       </c>
       <c r="C1229" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -22262,7 +22262,7 @@
       </c>
       <c r="C1233" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22279,7 +22279,7 @@
       </c>
       <c r="C1234" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22296,7 +22296,7 @@
       </c>
       <c r="C1235" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22330,7 +22330,7 @@
       </c>
       <c r="C1237" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -22381,7 +22381,7 @@
       </c>
       <c r="C1240" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22398,7 +22398,7 @@
       </c>
       <c r="C1241" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22534,7 +22534,7 @@
       </c>
       <c r="C1249" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22670,7 +22670,7 @@
       </c>
       <c r="C1257" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22687,7 +22687,7 @@
       </c>
       <c r="C1258" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22721,7 +22721,7 @@
       </c>
       <c r="C1260" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22772,7 +22772,7 @@
       </c>
       <c r="C1263" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -22823,7 +22823,7 @@
       </c>
       <c r="C1266" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -22840,7 +22840,7 @@
       </c>
       <c r="C1267" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -22874,7 +22874,7 @@
       </c>
       <c r="C1269" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -22908,7 +22908,7 @@
       </c>
       <c r="C1271" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -23027,7 +23027,7 @@
       </c>
       <c r="C1278" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -23044,7 +23044,7 @@
       </c>
       <c r="C1279" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -23095,7 +23095,7 @@
       </c>
       <c r="C1282" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -23316,7 +23316,7 @@
       </c>
       <c r="C1295" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -23333,7 +23333,7 @@
       </c>
       <c r="C1296" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -23350,7 +23350,7 @@
       </c>
       <c r="C1297" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -23401,7 +23401,7 @@
       </c>
       <c r="C1300" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -23877,7 +23877,7 @@
       </c>
       <c r="C1328" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -23928,7 +23928,7 @@
       </c>
       <c r="C1331" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -24302,7 +24302,7 @@
       </c>
       <c r="C1353" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -24370,7 +24370,7 @@
       </c>
       <c r="C1357" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -24523,7 +24523,7 @@
       </c>
       <c r="C1366" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -24557,7 +24557,7 @@
       </c>
       <c r="C1368" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -24812,7 +24812,7 @@
       </c>
       <c r="C1383" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -25050,7 +25050,7 @@
       </c>
       <c r="C1397" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -25118,7 +25118,7 @@
       </c>
       <c r="C1401" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -25169,7 +25169,7 @@
       </c>
       <c r="C1404" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -25288,7 +25288,7 @@
       </c>
       <c r="C1411" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25492,7 +25492,7 @@
       </c>
       <c r="C1423" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -25509,7 +25509,7 @@
       </c>
       <c r="C1424" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -25696,7 +25696,7 @@
       </c>
       <c r="C1435" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -25730,7 +25730,7 @@
       </c>
       <c r="C1437" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -25747,7 +25747,7 @@
       </c>
       <c r="C1438" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -25798,7 +25798,7 @@
       </c>
       <c r="C1441" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -25866,7 +25866,7 @@
       </c>
       <c r="C1445" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25951,7 +25951,7 @@
       </c>
       <c r="C1450" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26019,7 +26019,7 @@
       </c>
       <c r="C1454" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -26087,7 +26087,7 @@
       </c>
       <c r="C1458" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -26172,7 +26172,7 @@
       </c>
       <c r="C1463" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -26240,7 +26240,7 @@
       </c>
       <c r="C1467" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26291,7 +26291,7 @@
       </c>
       <c r="C1470" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26342,7 +26342,7 @@
       </c>
       <c r="C1473" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -26410,7 +26410,7 @@
       </c>
       <c r="C1477" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -26427,7 +26427,7 @@
       </c>
       <c r="C1478" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -26478,7 +26478,7 @@
       </c>
       <c r="C1481" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26529,7 +26529,7 @@
       </c>
       <c r="C1484" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26614,7 +26614,7 @@
       </c>
       <c r="C1489" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -26733,7 +26733,7 @@
       </c>
       <c r="C1496" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26767,7 +26767,7 @@
       </c>
       <c r="C1498" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
